--- a/data/members.xlsx
+++ b/data/members.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyCreation\Web\Gathering_Island\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Confidential\Gathering_Island\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{773F4084-95D3-471D-851A-C4E83F03FD2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC2E2C2B-B8A9-432B-9F75-9E732BD336BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-15" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="members" sheetId="1" r:id="rId1"/>
@@ -85,7 +85,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="718" uniqueCount="324">
   <si>
     <t>null</t>
   </si>
@@ -97,10 +97,6 @@
   </si>
   <si>
     <t>username</t>
-  </si>
-  <si>
-    <t>password_hash</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>email</t>
@@ -1069,6 +1065,16 @@
   </si>
   <si>
     <t>1979-05-11</t>
+  </si>
+  <si>
+    <t>member_password</t>
+  </si>
+  <si>
+    <t>aa123</t>
+  </si>
+  <si>
+    <t>aa123</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1173,7 +1179,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1209,18 +1215,8 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1506,7 +1502,8 @@
   <dimension ref="A1:Q160"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="3" width="19.75" style="1" customWidth="1"/>
+    <col min="1" max="2" width="19.75" style="1" customWidth="1"/>
+    <col min="3" max="3" width="27" style="1" customWidth="1"/>
     <col min="4" max="4" width="24" style="1" customWidth="1"/>
     <col min="5" max="7" width="19.75" style="1" customWidth="1"/>
     <col min="8" max="9" width="27" style="1" customWidth="1"/>
@@ -1516,38 +1513,37 @@
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="C1" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="D1" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="E1" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="F1" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="G1" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="H1" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="I1" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="I1" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
-      <c r="O1" s="14"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+      <c r="M1" s="8"/>
+      <c r="N1" s="8"/>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
@@ -1557,45 +1553,44 @@
         <v>3</v>
       </c>
       <c r="C2" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="D2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="E2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="F2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="G2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="H2" s="5" t="s">
         <v>8</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>9</v>
       </c>
       <c r="I2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="J2" s="15"/>
-      <c r="K2" s="15"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="15"/>
-      <c r="N2" s="15"/>
-      <c r="O2" s="14"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>1</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>323</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>19</v>
-      </c>
-      <c r="C3" s="2">
-        <v>123</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>20</v>
       </c>
       <c r="E3" s="2">
         <v>1</v>
@@ -1604,20 +1599,20 @@
         <v>0</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="J3" s="13"/>
-      <c r="K3" s="15"/>
-      <c r="L3" s="15"/>
-      <c r="M3" s="15"/>
-      <c r="N3" s="15"/>
-      <c r="O3" s="16"/>
+        <v>24</v>
+      </c>
+      <c r="J3" s="8"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3"/>
+      <c r="O3" s="11"/>
       <c r="P3" s="11"/>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.3">
@@ -1625,13 +1620,13 @@
         <v>2</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="C4" s="2">
-        <v>123</v>
+        <v>124</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>323</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E4" s="2">
         <v>1</v>
@@ -1640,20 +1635,20 @@
         <v>0</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J4" s="13"/>
-      <c r="K4" s="15"/>
-      <c r="L4" s="15"/>
-      <c r="M4" s="15"/>
-      <c r="N4" s="15"/>
-      <c r="O4" s="17"/>
+        <v>22</v>
+      </c>
+      <c r="J4" s="8"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="3"/>
+      <c r="N4" s="3"/>
+      <c r="O4" s="7"/>
       <c r="P4" s="7"/>
       <c r="Q4" s="7"/>
     </row>
@@ -1662,13 +1657,13 @@
         <v>3</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="C5" s="2">
-        <v>123</v>
+        <v>125</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E5" s="2">
         <v>1</v>
@@ -1677,13 +1672,13 @@
         <v>0</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J5" s="8"/>
       <c r="K5" s="3"/>
@@ -1699,13 +1694,13 @@
         <v>4</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="C6" s="2">
-        <v>123</v>
+        <v>126</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E6" s="2">
         <v>1</v>
@@ -1714,13 +1709,13 @@
         <v>0</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J6" s="8"/>
       <c r="K6" s="3"/>
@@ -1736,13 +1731,13 @@
         <v>5</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="C7" s="2">
-        <v>123</v>
+        <v>127</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E7" s="2">
         <v>1</v>
@@ -1751,13 +1746,13 @@
         <v>0</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J7" s="8"/>
       <c r="K7" s="3"/>
@@ -1770,13 +1765,13 @@
         <v>6</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="C8" s="2">
-        <v>123</v>
+        <v>128</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E8" s="2">
         <v>1</v>
@@ -1785,13 +1780,13 @@
         <v>0</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J8" s="8"/>
       <c r="K8" s="3"/>
@@ -1807,13 +1802,13 @@
         <v>7</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="C9" s="2">
-        <v>123</v>
+        <v>129</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E9" s="2">
         <v>1</v>
@@ -1822,13 +1817,13 @@
         <v>0</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J9" s="8"/>
       <c r="K9" s="3"/>
@@ -1844,13 +1839,13 @@
         <v>8</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="C10" s="2">
-        <v>123</v>
+        <v>130</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E10" s="2">
         <v>1</v>
@@ -1859,13 +1854,13 @@
         <v>0</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J10" s="8"/>
       <c r="K10" s="3"/>
@@ -1881,13 +1876,13 @@
         <v>9</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="C11" s="2">
-        <v>123</v>
+        <v>131</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E11" s="2">
         <v>1</v>
@@ -1896,13 +1891,13 @@
         <v>0</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J11" s="8"/>
       <c r="K11" s="3"/>
@@ -1918,13 +1913,13 @@
         <v>10</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="C12" s="2">
-        <v>123</v>
+        <v>132</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E12" s="2">
         <v>1</v>
@@ -1933,13 +1928,13 @@
         <v>0</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J12" s="8"/>
       <c r="K12" s="3"/>
@@ -1955,13 +1950,13 @@
         <v>11</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="C13" s="2">
-        <v>123</v>
+        <v>133</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E13" s="2">
         <v>1</v>
@@ -1970,13 +1965,13 @@
         <v>0</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J13" s="8"/>
       <c r="K13" s="3"/>
@@ -1992,13 +1987,13 @@
         <v>12</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="C14" s="2">
-        <v>123</v>
+        <v>134</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E14" s="2">
         <v>1</v>
@@ -2007,13 +2002,13 @@
         <v>0</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J14" s="8"/>
       <c r="K14" s="3"/>
@@ -2029,13 +2024,13 @@
         <v>13</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="C15" s="2">
-        <v>123</v>
+        <v>135</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E15" s="2">
         <v>1</v>
@@ -2044,13 +2039,13 @@
         <v>0</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J15" s="8"/>
       <c r="K15" s="3"/>
@@ -2066,13 +2061,13 @@
         <v>14</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="C16" s="2">
-        <v>123</v>
+        <v>136</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E16" s="2">
         <v>1</v>
@@ -2081,13 +2076,13 @@
         <v>0</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J16" s="8"/>
       <c r="K16" s="3"/>
@@ -2103,13 +2098,13 @@
         <v>15</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="C17" s="2">
-        <v>123</v>
+        <v>137</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E17" s="2">
         <v>1</v>
@@ -2118,13 +2113,13 @@
         <v>0</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J17" s="8"/>
       <c r="K17" s="3"/>
@@ -2140,13 +2135,13 @@
         <v>16</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="C18" s="2">
-        <v>123</v>
+        <v>138</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E18" s="2">
         <v>1</v>
@@ -2155,13 +2150,13 @@
         <v>0</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J18" s="8"/>
       <c r="K18" s="3"/>
@@ -2177,13 +2172,13 @@
         <v>17</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="C19" s="2">
-        <v>123</v>
+        <v>139</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E19" s="2">
         <v>1</v>
@@ -2192,13 +2187,13 @@
         <v>0</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J19" s="8"/>
       <c r="K19" s="3"/>
@@ -2214,13 +2209,13 @@
         <v>18</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="C20" s="2">
-        <v>123</v>
+        <v>140</v>
+      </c>
+      <c r="C20" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E20" s="2">
         <v>1</v>
@@ -2229,13 +2224,13 @@
         <v>0</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J20" s="8"/>
       <c r="K20" s="3"/>
@@ -2251,13 +2246,13 @@
         <v>19</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="C21" s="2">
-        <v>123</v>
+        <v>141</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E21" s="2">
         <v>1</v>
@@ -2266,13 +2261,13 @@
         <v>0</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J21" s="8"/>
       <c r="K21" s="3"/>
@@ -2288,13 +2283,13 @@
         <v>20</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="C22" s="2">
-        <v>123</v>
+        <v>142</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E22" s="2">
         <v>1</v>
@@ -2303,13 +2298,13 @@
         <v>0</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J22" s="8"/>
       <c r="K22" s="3"/>
@@ -2325,13 +2320,13 @@
         <v>21</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="C23" s="2">
-        <v>123</v>
+        <v>143</v>
+      </c>
+      <c r="C23" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E23" s="2">
         <v>1</v>
@@ -2340,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J23" s="8"/>
       <c r="K23" s="3"/>
@@ -2362,13 +2357,13 @@
         <v>22</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="C24" s="2">
-        <v>123</v>
+        <v>144</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E24" s="2">
         <v>1</v>
@@ -2377,13 +2372,13 @@
         <v>0</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J24" s="8"/>
       <c r="K24" s="3"/>
@@ -2399,13 +2394,13 @@
         <v>23</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="C25" s="2">
-        <v>123</v>
+        <v>145</v>
+      </c>
+      <c r="C25" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E25" s="2">
         <v>1</v>
@@ -2414,13 +2409,13 @@
         <v>0</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J25" s="8"/>
       <c r="K25" s="3"/>
@@ -2436,13 +2431,13 @@
         <v>24</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="C26" s="2">
-        <v>123</v>
+        <v>146</v>
+      </c>
+      <c r="C26" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E26" s="2">
         <v>1</v>
@@ -2451,13 +2446,13 @@
         <v>0</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J26" s="8"/>
       <c r="K26" s="3"/>
@@ -2473,13 +2468,13 @@
         <v>25</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="C27" s="2">
-        <v>123</v>
+        <v>147</v>
+      </c>
+      <c r="C27" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E27" s="2">
         <v>1</v>
@@ -2488,13 +2483,13 @@
         <v>0</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J27" s="8"/>
       <c r="K27" s="3"/>
@@ -2510,13 +2505,13 @@
         <v>26</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="C28" s="2">
-        <v>123</v>
+        <v>148</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E28" s="2">
         <v>1</v>
@@ -2525,13 +2520,13 @@
         <v>0</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J28" s="8"/>
       <c r="K28" s="3"/>
@@ -2547,13 +2542,13 @@
         <v>27</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="C29" s="2">
-        <v>123</v>
+        <v>149</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E29" s="2">
         <v>1</v>
@@ -2562,13 +2557,13 @@
         <v>0</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J29" s="8"/>
       <c r="K29" s="3"/>
@@ -2584,13 +2579,13 @@
         <v>28</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="C30" s="2">
-        <v>123</v>
+        <v>150</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E30" s="2">
         <v>1</v>
@@ -2599,13 +2594,13 @@
         <v>0</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J30" s="8"/>
       <c r="K30" s="3"/>
@@ -2621,13 +2616,13 @@
         <v>29</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="C31" s="2">
-        <v>123</v>
+        <v>151</v>
+      </c>
+      <c r="C31" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E31" s="2">
         <v>1</v>
@@ -2636,13 +2631,13 @@
         <v>0</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J31" s="8"/>
       <c r="K31" s="3"/>
@@ -2658,13 +2653,13 @@
         <v>30</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="C32" s="2">
-        <v>123</v>
+        <v>152</v>
+      </c>
+      <c r="C32" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E32" s="2">
         <v>1</v>
@@ -2673,13 +2668,13 @@
         <v>0</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J32" s="8"/>
       <c r="K32" s="3"/>
@@ -2695,13 +2690,13 @@
         <v>31</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="C33" s="2">
-        <v>123</v>
+        <v>153</v>
+      </c>
+      <c r="C33" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E33" s="2">
         <v>1</v>
@@ -2710,13 +2705,13 @@
         <v>0</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J33" s="8"/>
       <c r="K33" s="3"/>
@@ -2732,13 +2727,13 @@
         <v>32</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="C34" s="2">
-        <v>123</v>
+        <v>154</v>
+      </c>
+      <c r="C34" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E34" s="2">
         <v>1</v>
@@ -2747,13 +2742,13 @@
         <v>0</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J34" s="8"/>
       <c r="K34" s="3"/>
@@ -2769,13 +2764,13 @@
         <v>33</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="C35" s="2">
-        <v>123</v>
+        <v>155</v>
+      </c>
+      <c r="C35" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E35" s="2">
         <v>1</v>
@@ -2784,13 +2779,13 @@
         <v>0</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J35" s="8"/>
       <c r="K35" s="3"/>
@@ -2806,13 +2801,13 @@
         <v>34</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="C36" s="2">
-        <v>123</v>
+        <v>156</v>
+      </c>
+      <c r="C36" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E36" s="2">
         <v>1</v>
@@ -2821,13 +2816,13 @@
         <v>0</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J36" s="8"/>
       <c r="K36" s="3"/>
@@ -2843,13 +2838,13 @@
         <v>35</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="C37" s="2">
-        <v>123</v>
+        <v>157</v>
+      </c>
+      <c r="C37" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E37" s="2">
         <v>1</v>
@@ -2858,13 +2853,13 @@
         <v>0</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J37" s="8"/>
       <c r="K37" s="3"/>
@@ -2880,13 +2875,13 @@
         <v>36</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="C38" s="2">
-        <v>123</v>
+        <v>158</v>
+      </c>
+      <c r="C38" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E38" s="2">
         <v>1</v>
@@ -2895,13 +2890,13 @@
         <v>0</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J38" s="8"/>
       <c r="K38" s="3"/>
@@ -2917,13 +2912,13 @@
         <v>37</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="C39" s="2">
-        <v>123</v>
+        <v>159</v>
+      </c>
+      <c r="C39" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E39" s="2">
         <v>1</v>
@@ -2932,13 +2927,13 @@
         <v>0</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J39" s="8"/>
       <c r="K39" s="3"/>
@@ -2954,13 +2949,13 @@
         <v>38</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="C40" s="2">
-        <v>123</v>
+        <v>160</v>
+      </c>
+      <c r="C40" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E40" s="2">
         <v>1</v>
@@ -2969,13 +2964,13 @@
         <v>0</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J40" s="8"/>
       <c r="K40" s="3"/>
@@ -2991,13 +2986,13 @@
         <v>39</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="C41" s="2">
-        <v>123</v>
+        <v>161</v>
+      </c>
+      <c r="C41" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E41" s="2">
         <v>1</v>
@@ -3006,13 +3001,13 @@
         <v>0</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J41" s="8"/>
       <c r="K41" s="3"/>
@@ -3028,13 +3023,13 @@
         <v>40</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="C42" s="2">
-        <v>123</v>
+        <v>162</v>
+      </c>
+      <c r="C42" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E42" s="2">
         <v>1</v>
@@ -3043,13 +3038,13 @@
         <v>0</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J42" s="8"/>
       <c r="K42" s="3"/>
@@ -3065,13 +3060,13 @@
         <v>41</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="C43" s="2">
-        <v>123</v>
+        <v>163</v>
+      </c>
+      <c r="C43" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E43" s="2">
         <v>1</v>
@@ -3080,13 +3075,13 @@
         <v>0</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J43" s="8"/>
       <c r="K43" s="3"/>
@@ -3102,13 +3097,13 @@
         <v>42</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="C44" s="2">
-        <v>123</v>
+        <v>164</v>
+      </c>
+      <c r="C44" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E44" s="2">
         <v>1</v>
@@ -3117,13 +3112,13 @@
         <v>0</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J44" s="8"/>
       <c r="K44" s="3"/>
@@ -3139,13 +3134,13 @@
         <v>43</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="C45" s="2">
-        <v>123</v>
+        <v>165</v>
+      </c>
+      <c r="C45" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E45" s="2">
         <v>1</v>
@@ -3154,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J45" s="8"/>
       <c r="K45" s="3"/>
@@ -3176,13 +3171,13 @@
         <v>44</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="C46" s="2">
-        <v>123</v>
+        <v>166</v>
+      </c>
+      <c r="C46" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E46" s="2">
         <v>1</v>
@@ -3191,13 +3186,13 @@
         <v>0</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J46" s="8"/>
       <c r="K46" s="3"/>
@@ -3213,13 +3208,13 @@
         <v>45</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="C47" s="2">
-        <v>123</v>
+        <v>167</v>
+      </c>
+      <c r="C47" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E47" s="2">
         <v>1</v>
@@ -3228,13 +3223,13 @@
         <v>0</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J47" s="8"/>
       <c r="K47" s="3"/>
@@ -3250,13 +3245,13 @@
         <v>46</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="C48" s="2">
-        <v>123</v>
+        <v>168</v>
+      </c>
+      <c r="C48" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E48" s="2">
         <v>1</v>
@@ -3265,13 +3260,13 @@
         <v>0</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J48" s="8"/>
       <c r="K48" s="3"/>
@@ -3287,13 +3282,13 @@
         <v>47</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="C49" s="2">
-        <v>123</v>
+        <v>169</v>
+      </c>
+      <c r="C49" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E49" s="2">
         <v>1</v>
@@ -3302,13 +3297,13 @@
         <v>0</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J49" s="8"/>
       <c r="K49" s="3"/>
@@ -3324,13 +3319,13 @@
         <v>48</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="C50" s="2">
-        <v>123</v>
+        <v>170</v>
+      </c>
+      <c r="C50" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E50" s="2">
         <v>1</v>
@@ -3339,13 +3334,13 @@
         <v>0</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J50" s="8"/>
       <c r="K50" s="3"/>
@@ -3361,13 +3356,13 @@
         <v>49</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="C51" s="2">
-        <v>123</v>
+        <v>171</v>
+      </c>
+      <c r="C51" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E51" s="2">
         <v>1</v>
@@ -3376,13 +3371,13 @@
         <v>0</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J51" s="8"/>
       <c r="K51" s="3"/>
@@ -3398,13 +3393,13 @@
         <v>50</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="C52" s="2">
-        <v>123</v>
+        <v>172</v>
+      </c>
+      <c r="C52" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E52" s="2">
         <v>1</v>
@@ -3413,13 +3408,13 @@
         <v>0</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J52" s="8"/>
       <c r="K52" s="3"/>
@@ -3435,13 +3430,13 @@
         <v>51</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="C53" s="2">
-        <v>123</v>
+        <v>173</v>
+      </c>
+      <c r="C53" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E53" s="2">
         <v>2</v>
@@ -3450,13 +3445,13 @@
         <v>0</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J53" s="8"/>
       <c r="K53" s="3"/>
@@ -3472,13 +3467,13 @@
         <v>52</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="C54" s="2">
-        <v>123</v>
+        <v>174</v>
+      </c>
+      <c r="C54" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E54" s="2">
         <v>2</v>
@@ -3487,13 +3482,13 @@
         <v>0</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J54" s="8"/>
       <c r="K54" s="3"/>
@@ -3509,13 +3504,13 @@
         <v>53</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="C55" s="2">
-        <v>123</v>
+        <v>175</v>
+      </c>
+      <c r="C55" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E55" s="2">
         <v>2</v>
@@ -3524,13 +3519,13 @@
         <v>0</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J55" s="8"/>
       <c r="K55" s="3"/>
@@ -3546,13 +3541,13 @@
         <v>54</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="C56" s="2">
-        <v>123</v>
+        <v>176</v>
+      </c>
+      <c r="C56" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E56" s="2">
         <v>2</v>
@@ -3561,13 +3556,13 @@
         <v>0</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J56" s="8"/>
       <c r="K56" s="3"/>
@@ -3583,13 +3578,13 @@
         <v>55</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="C57" s="2">
-        <v>123</v>
+        <v>177</v>
+      </c>
+      <c r="C57" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E57" s="2">
         <v>2</v>
@@ -3598,13 +3593,13 @@
         <v>0</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J57" s="8"/>
       <c r="K57" s="3"/>
@@ -3620,13 +3615,13 @@
         <v>56</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="C58" s="2">
+        <v>178</v>
+      </c>
+      <c r="C58" s="13" t="s">
+        <v>322</v>
+      </c>
+      <c r="D58" s="2" t="s">
         <v>123</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>124</v>
       </c>
       <c r="E58" s="2">
         <v>2</v>
@@ -3635,13 +3630,13 @@
         <v>0</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J58" s="8"/>
       <c r="K58" s="3"/>
@@ -3657,13 +3652,13 @@
         <v>57</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="C59" s="2">
-        <v>123</v>
+        <v>179</v>
+      </c>
+      <c r="C59" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E59" s="2">
         <v>2</v>
@@ -3672,13 +3667,13 @@
         <v>0</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J59" s="8"/>
       <c r="K59" s="3"/>
@@ -3694,13 +3689,13 @@
         <v>58</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="C60" s="2">
-        <v>123</v>
+        <v>180</v>
+      </c>
+      <c r="C60" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E60" s="2">
         <v>2</v>
@@ -3709,13 +3704,13 @@
         <v>0</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J60" s="8"/>
       <c r="K60" s="3"/>
@@ -3731,13 +3726,13 @@
         <v>59</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="C61" s="2">
-        <v>123</v>
+        <v>181</v>
+      </c>
+      <c r="C61" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E61" s="2">
         <v>2</v>
@@ -3746,13 +3741,13 @@
         <v>0</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J61" s="8"/>
       <c r="K61" s="3"/>
@@ -3768,13 +3763,13 @@
         <v>60</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="C62" s="2">
-        <v>123</v>
+        <v>182</v>
+      </c>
+      <c r="C62" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E62" s="2">
         <v>2</v>
@@ -3783,13 +3778,13 @@
         <v>0</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J62" s="8"/>
       <c r="K62" s="3"/>
@@ -3805,13 +3800,13 @@
         <v>61</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="C63" s="2">
-        <v>123</v>
+        <v>183</v>
+      </c>
+      <c r="C63" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E63" s="2">
         <v>2</v>
@@ -3820,13 +3815,13 @@
         <v>0</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J63" s="8"/>
       <c r="K63" s="3"/>
@@ -3842,13 +3837,13 @@
         <v>62</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="C64" s="2">
-        <v>123</v>
+        <v>184</v>
+      </c>
+      <c r="C64" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E64" s="2">
         <v>2</v>
@@ -3857,13 +3852,13 @@
         <v>0</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J64" s="8"/>
       <c r="K64" s="3"/>
@@ -3879,13 +3874,13 @@
         <v>63</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="C65" s="2">
-        <v>123</v>
+        <v>185</v>
+      </c>
+      <c r="C65" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E65" s="2">
         <v>2</v>
@@ -3894,13 +3889,13 @@
         <v>0</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J65" s="8"/>
       <c r="K65" s="3"/>
@@ -3916,13 +3911,13 @@
         <v>64</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="C66" s="2">
-        <v>123</v>
+        <v>186</v>
+      </c>
+      <c r="C66" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E66" s="2">
         <v>2</v>
@@ -3931,13 +3926,13 @@
         <v>0</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J66" s="8"/>
       <c r="K66" s="3"/>
@@ -3953,13 +3948,13 @@
         <v>65</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="C67" s="2">
-        <v>123</v>
+        <v>187</v>
+      </c>
+      <c r="C67" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E67" s="2">
         <v>2</v>
@@ -3968,13 +3963,13 @@
         <v>0</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J67" s="8"/>
       <c r="K67" s="3"/>
@@ -3990,13 +3985,13 @@
         <v>66</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="C68" s="2">
-        <v>123</v>
+        <v>188</v>
+      </c>
+      <c r="C68" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E68" s="2">
         <v>2</v>
@@ -4005,13 +4000,13 @@
         <v>0</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J68" s="8"/>
       <c r="K68" s="3"/>
@@ -4027,13 +4022,13 @@
         <v>67</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="C69" s="2">
-        <v>123</v>
+        <v>189</v>
+      </c>
+      <c r="C69" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E69" s="2">
         <v>2</v>
@@ -4042,13 +4037,13 @@
         <v>0</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J69" s="8"/>
       <c r="K69" s="3"/>
@@ -4064,13 +4059,13 @@
         <v>68</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="C70" s="2">
-        <v>123</v>
+        <v>190</v>
+      </c>
+      <c r="C70" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E70" s="2">
         <v>2</v>
@@ -4079,13 +4074,13 @@
         <v>0</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J70" s="8"/>
       <c r="K70" s="3"/>
@@ -4101,13 +4096,13 @@
         <v>69</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="C71" s="2">
-        <v>123</v>
+        <v>191</v>
+      </c>
+      <c r="C71" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E71" s="2">
         <v>2</v>
@@ -4116,13 +4111,13 @@
         <v>0</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J71" s="8"/>
       <c r="K71" s="3"/>
@@ -4138,13 +4133,13 @@
         <v>70</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="C72" s="2">
-        <v>123</v>
+        <v>192</v>
+      </c>
+      <c r="C72" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E72" s="2">
         <v>2</v>
@@ -4153,13 +4148,13 @@
         <v>0</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J72" s="8"/>
       <c r="K72" s="3"/>
@@ -4175,13 +4170,13 @@
         <v>71</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="C73" s="2">
-        <v>123</v>
+        <v>193</v>
+      </c>
+      <c r="C73" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E73" s="2">
         <v>2</v>
@@ -4190,13 +4185,13 @@
         <v>0</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J73" s="8"/>
       <c r="K73" s="3"/>
@@ -4212,13 +4207,13 @@
         <v>72</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="C74" s="2">
-        <v>123</v>
+        <v>194</v>
+      </c>
+      <c r="C74" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E74" s="2">
         <v>2</v>
@@ -4227,13 +4222,13 @@
         <v>0</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J74" s="8"/>
       <c r="K74" s="3"/>
@@ -4249,13 +4244,13 @@
         <v>73</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="C75" s="2">
-        <v>123</v>
+        <v>195</v>
+      </c>
+      <c r="C75" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E75" s="2">
         <v>2</v>
@@ -4264,13 +4259,13 @@
         <v>0</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J75" s="8"/>
       <c r="K75" s="3"/>
@@ -4286,13 +4281,13 @@
         <v>74</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="C76" s="2">
-        <v>123</v>
+        <v>196</v>
+      </c>
+      <c r="C76" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E76" s="2">
         <v>2</v>
@@ -4301,13 +4296,13 @@
         <v>0</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J76" s="8"/>
       <c r="K76" s="3"/>
@@ -4323,13 +4318,13 @@
         <v>75</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="C77" s="2">
-        <v>123</v>
+        <v>197</v>
+      </c>
+      <c r="C77" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E77" s="2">
         <v>2</v>
@@ -4338,13 +4333,13 @@
         <v>0</v>
       </c>
       <c r="G77" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J77" s="8"/>
       <c r="K77" s="3"/>
@@ -4360,13 +4355,13 @@
         <v>76</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="C78" s="2">
-        <v>123</v>
+        <v>198</v>
+      </c>
+      <c r="C78" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E78" s="2">
         <v>2</v>
@@ -4375,13 +4370,13 @@
         <v>0</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J78" s="8"/>
       <c r="K78" s="3"/>
@@ -4397,13 +4392,13 @@
         <v>77</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="C79" s="2">
-        <v>123</v>
+        <v>199</v>
+      </c>
+      <c r="C79" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E79" s="2">
         <v>2</v>
@@ -4412,13 +4407,13 @@
         <v>0</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J79" s="8"/>
       <c r="K79" s="3"/>
@@ -4434,13 +4429,13 @@
         <v>78</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="C80" s="2">
-        <v>123</v>
+        <v>200</v>
+      </c>
+      <c r="C80" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E80" s="2">
         <v>2</v>
@@ -4449,13 +4444,13 @@
         <v>0</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J80" s="8"/>
       <c r="K80" s="3"/>
@@ -4471,13 +4466,13 @@
         <v>79</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="C81" s="2">
-        <v>123</v>
+        <v>201</v>
+      </c>
+      <c r="C81" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E81" s="2">
         <v>2</v>
@@ -4486,13 +4481,13 @@
         <v>0</v>
       </c>
       <c r="G81" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J81" s="8"/>
       <c r="K81" s="3"/>
@@ -4508,13 +4503,13 @@
         <v>80</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="C82" s="2">
-        <v>123</v>
+        <v>202</v>
+      </c>
+      <c r="C82" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E82" s="2">
         <v>2</v>
@@ -4523,13 +4518,13 @@
         <v>0</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J82" s="8"/>
       <c r="K82" s="3"/>
@@ -4545,13 +4540,13 @@
         <v>81</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="C83" s="2">
-        <v>123</v>
+        <v>203</v>
+      </c>
+      <c r="C83" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E83" s="2">
         <v>2</v>
@@ -4560,13 +4555,13 @@
         <v>0</v>
       </c>
       <c r="G83" s="3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J83" s="8"/>
       <c r="K83" s="3"/>
@@ -4582,13 +4577,13 @@
         <v>82</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="C84" s="2">
-        <v>123</v>
+        <v>204</v>
+      </c>
+      <c r="C84" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E84" s="2">
         <v>2</v>
@@ -4597,13 +4592,13 @@
         <v>0</v>
       </c>
       <c r="G84" s="3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J84" s="8"/>
       <c r="K84" s="3"/>
@@ -4619,13 +4614,13 @@
         <v>83</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="C85" s="2">
-        <v>123</v>
+        <v>205</v>
+      </c>
+      <c r="C85" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E85" s="2">
         <v>2</v>
@@ -4634,13 +4629,13 @@
         <v>0</v>
       </c>
       <c r="G85" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J85" s="8"/>
       <c r="K85" s="3"/>
@@ -4656,13 +4651,13 @@
         <v>84</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="C86" s="2">
-        <v>123</v>
+        <v>206</v>
+      </c>
+      <c r="C86" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E86" s="2">
         <v>2</v>
@@ -4671,13 +4666,13 @@
         <v>0</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J86" s="8"/>
       <c r="K86" s="3"/>
@@ -4693,13 +4688,13 @@
         <v>85</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="C87" s="2">
-        <v>123</v>
+        <v>207</v>
+      </c>
+      <c r="C87" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E87" s="2">
         <v>2</v>
@@ -4708,13 +4703,13 @@
         <v>0</v>
       </c>
       <c r="G87" s="3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J87" s="8"/>
       <c r="K87" s="3"/>
@@ -4730,13 +4725,13 @@
         <v>86</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="C88" s="2">
-        <v>123</v>
+        <v>208</v>
+      </c>
+      <c r="C88" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E88" s="2">
         <v>2</v>
@@ -4745,13 +4740,13 @@
         <v>0</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J88" s="8"/>
       <c r="K88" s="3"/>
@@ -4767,13 +4762,13 @@
         <v>87</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="C89" s="2">
-        <v>123</v>
+        <v>209</v>
+      </c>
+      <c r="C89" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E89" s="2">
         <v>2</v>
@@ -4782,13 +4777,13 @@
         <v>0</v>
       </c>
       <c r="G89" s="3" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J89" s="8"/>
       <c r="K89" s="3"/>
@@ -4804,13 +4799,13 @@
         <v>88</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="C90" s="2">
-        <v>123</v>
+        <v>210</v>
+      </c>
+      <c r="C90" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E90" s="2">
         <v>2</v>
@@ -4819,13 +4814,13 @@
         <v>0</v>
       </c>
       <c r="G90" s="3" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J90" s="8"/>
       <c r="K90" s="3"/>
@@ -4841,13 +4836,13 @@
         <v>89</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="C91" s="2">
-        <v>123</v>
+        <v>211</v>
+      </c>
+      <c r="C91" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E91" s="2">
         <v>2</v>
@@ -4856,13 +4851,13 @@
         <v>0</v>
       </c>
       <c r="G91" s="3" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J91" s="8"/>
       <c r="K91" s="3"/>
@@ -4878,13 +4873,13 @@
         <v>90</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="C92" s="2">
-        <v>123</v>
+        <v>212</v>
+      </c>
+      <c r="C92" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E92" s="2">
         <v>2</v>
@@ -4893,13 +4888,13 @@
         <v>0</v>
       </c>
       <c r="G92" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J92" s="8"/>
       <c r="K92" s="3"/>
@@ -4915,13 +4910,13 @@
         <v>91</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="C93" s="2">
-        <v>123</v>
+        <v>213</v>
+      </c>
+      <c r="C93" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E93" s="2">
         <v>2</v>
@@ -4930,13 +4925,13 @@
         <v>0</v>
       </c>
       <c r="G93" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J93" s="8"/>
       <c r="K93" s="3"/>
@@ -4952,13 +4947,13 @@
         <v>92</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="C94" s="2">
-        <v>123</v>
+        <v>214</v>
+      </c>
+      <c r="C94" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E94" s="2">
         <v>2</v>
@@ -4967,13 +4962,13 @@
         <v>0</v>
       </c>
       <c r="G94" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J94" s="8"/>
       <c r="K94" s="3"/>
@@ -4989,13 +4984,13 @@
         <v>93</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="C95" s="2">
-        <v>123</v>
+        <v>215</v>
+      </c>
+      <c r="C95" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E95" s="2">
         <v>2</v>
@@ -5004,13 +4999,13 @@
         <v>0</v>
       </c>
       <c r="G95" s="3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J95" s="8"/>
       <c r="K95" s="3"/>
@@ -5026,13 +5021,13 @@
         <v>94</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="C96" s="2">
-        <v>123</v>
+        <v>216</v>
+      </c>
+      <c r="C96" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E96" s="2">
         <v>2</v>
@@ -5041,13 +5036,13 @@
         <v>0</v>
       </c>
       <c r="G96" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J96" s="8"/>
       <c r="K96" s="3"/>
@@ -5063,13 +5058,13 @@
         <v>95</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="C97" s="2">
-        <v>123</v>
+        <v>217</v>
+      </c>
+      <c r="C97" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E97" s="2">
         <v>2</v>
@@ -5078,13 +5073,13 @@
         <v>0</v>
       </c>
       <c r="G97" s="3" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J97" s="8"/>
       <c r="K97" s="3"/>
@@ -5100,13 +5095,13 @@
         <v>96</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="C98" s="2">
-        <v>123</v>
+        <v>218</v>
+      </c>
+      <c r="C98" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E98" s="2">
         <v>2</v>
@@ -5115,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="G98" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J98" s="8"/>
       <c r="K98" s="3"/>
@@ -5137,13 +5132,13 @@
         <v>97</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="C99" s="2">
-        <v>123</v>
+        <v>219</v>
+      </c>
+      <c r="C99" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E99" s="2">
         <v>2</v>
@@ -5152,13 +5147,13 @@
         <v>0</v>
       </c>
       <c r="G99" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I99" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J99" s="8"/>
       <c r="K99" s="3"/>
@@ -5171,13 +5166,13 @@
         <v>98</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="C100" s="2">
-        <v>123</v>
+        <v>220</v>
+      </c>
+      <c r="C100" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E100" s="2">
         <v>2</v>
@@ -5186,13 +5181,13 @@
         <v>0</v>
       </c>
       <c r="G100" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I100" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J100" s="8"/>
       <c r="K100" s="3"/>
@@ -5205,13 +5200,13 @@
         <v>99</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="C101" s="2">
-        <v>123</v>
+        <v>221</v>
+      </c>
+      <c r="C101" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E101" s="2">
         <v>2</v>
@@ -5220,13 +5215,13 @@
         <v>0</v>
       </c>
       <c r="G101" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I101" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J101" s="8"/>
       <c r="K101" s="3"/>
@@ -5239,13 +5234,13 @@
         <v>100</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="C102" s="2">
-        <v>123</v>
+        <v>222</v>
+      </c>
+      <c r="C102" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E102" s="2">
         <v>2</v>
@@ -5254,13 +5249,13 @@
         <v>0</v>
       </c>
       <c r="G102" s="3" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I102" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J102" s="8"/>
       <c r="K102" s="3"/>
